--- a/1. Mastering Corel Excel Functions.xlsx
+++ b/1. Mastering Corel Excel Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trichyravis/Library/Mobile Documents/com~apple~CloudDocs/01. Ravis Academics/07. My Lectures Subject Wise/18. Financial Modelling /20. Claude Templates/63. Mastering Core Excel Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E530107-4E5F-0E46-8F02-7B2D203DAFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5540BE9-27EA-4C44-8B86-EFE8DC83C402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{B6D02A92-4BB0-4A40-B80F-1AB3D3CFBF1C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19420" activeTab="6" xr2:uid="{B6D02A92-4BB0-4A40-B80F-1AB3D3CFBF1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Contents" sheetId="11" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Math Extras" sheetId="10" r:id="rId11"/>
     <sheet name="Information &amp; Cell" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="627">
   <si>
     <t>Core Math Functions</t>
   </si>
@@ -1779,6 +1779,177 @@
   </si>
   <si>
     <t>11. Information &amp; Cell</t>
+  </si>
+  <si>
+    <t>LINEST</t>
+  </si>
+  <si>
+    <t>=LINEST(y, x)</t>
+  </si>
+  <si>
+    <t>=INDEX(LINEST(B5:I5,B4:I4),1,1)</t>
+  </si>
+  <si>
+    <t>Regression coefficients (here: slope)</t>
+  </si>
+  <si>
+    <t>LINEST – intercept</t>
+  </si>
+  <si>
+    <t>=INDEX(LINEST(y,x),1,2)</t>
+  </si>
+  <si>
+    <t>=INDEX(LINEST(B5:I5,B4:I4),1,2)</t>
+  </si>
+  <si>
+    <t>Y-intercept of the regression line</t>
+  </si>
+  <si>
+    <t>LINEST – R²</t>
+  </si>
+  <si>
+    <t>=INDEX(LINEST(y,x,,TRUE),3,1)</t>
+  </si>
+  <si>
+    <t>=INDEX(LINEST(B5:I5,B4:I4,TRUE,TRUE),3,1)</t>
+  </si>
+  <si>
+    <t>R² – goodness of fit (stats=TRUE)</t>
+  </si>
+  <si>
+    <t>LINEST – full array (spills below →)</t>
+  </si>
+  <si>
+    <t>5×2 stats block: row1 slope/intercept, row3 R²/se, etc.</t>
+  </si>
+  <si>
+    <t>Full LINEST output</t>
+  </si>
+  <si>
+    <t>← slope | intercept</t>
+  </si>
+  <si>
+    <t>← std err of slope | intercept</t>
+  </si>
+  <si>
+    <t>← R² | std err of y estimate</t>
+  </si>
+  <si>
+    <t>← F statistic | degrees of freedom</t>
+  </si>
+  <si>
+    <t>← regression SS | residual SS</t>
+  </si>
+  <si>
+    <t>Statistical Distribution Functions</t>
+  </si>
+  <si>
+    <t>NORM.DIST</t>
+  </si>
+  <si>
+    <t>=NORM.DIST(x, mean, sd, cum)</t>
+  </si>
+  <si>
+    <t>=NORM.DIST(160,AVERAGE(B5:I5),STDEV.S(B5:I5),TRUE)</t>
+  </si>
+  <si>
+    <t>Probability a value ≤ x (cumulative)</t>
+  </si>
+  <si>
+    <t>NORM.INV</t>
+  </si>
+  <si>
+    <t>=NORM.INV(prob, mean, sd)</t>
+  </si>
+  <si>
+    <t>=NORM.INV(0.9,AVERAGE(B5:I5),STDEV.S(B5:I5))</t>
+  </si>
+  <si>
+    <t>Value at a given cumulative probability</t>
+  </si>
+  <si>
+    <t>NORM.S.DIST</t>
+  </si>
+  <si>
+    <t>=NORM.S.DIST(z, cum)</t>
+  </si>
+  <si>
+    <t>=NORM.S.DIST(1.5,TRUE)</t>
+  </si>
+  <si>
+    <t>Standard normal probability for a z-score</t>
+  </si>
+  <si>
+    <t>NORM.S.INV</t>
+  </si>
+  <si>
+    <t>=NORM.S.INV(prob)</t>
+  </si>
+  <si>
+    <t>=NORM.S.INV(0.975)</t>
+  </si>
+  <si>
+    <t>Z-score for a cumulative probability</t>
+  </si>
+  <si>
+    <t>STANDARDIZE</t>
+  </si>
+  <si>
+    <t>=STANDARDIZE(x, mean, sd)</t>
+  </si>
+  <si>
+    <t>=STANDARDIZE(160,AVERAGE(B5:I5),STDEV.S(B5:I5))</t>
+  </si>
+  <si>
+    <t>Converts a value to a z-score</t>
+  </si>
+  <si>
+    <t>BINOM.DIST</t>
+  </si>
+  <si>
+    <t>=BINOM.DIST(s, trials, p, cum)</t>
+  </si>
+  <si>
+    <t>=BINOM.DIST(3,10,0.5,FALSE)</t>
+  </si>
+  <si>
+    <t>Probability of s successes in n trials</t>
+  </si>
+  <si>
+    <t>POISSON.DIST</t>
+  </si>
+  <si>
+    <t>=POISSON.DIST(x, mean, cum)</t>
+  </si>
+  <si>
+    <t>=POISSON.DIST(4,3,FALSE)</t>
+  </si>
+  <si>
+    <t>Probability of x events given a mean rate</t>
+  </si>
+  <si>
+    <t>EXPON.DIST</t>
+  </si>
+  <si>
+    <t>=EXPON.DIST(x, lambda, cum)</t>
+  </si>
+  <si>
+    <t>=EXPON.DIST(2,0.5,TRUE)</t>
+  </si>
+  <si>
+    <t>Cumulative probability for wait times</t>
+  </si>
+  <si>
+    <t>CONFIDENCE.NORM</t>
+  </si>
+  <si>
+    <t>=CONFIDENCE.NORM(alpha, sd, n)</t>
+  </si>
+  <si>
+    <t>=CONFIDENCE.NORM(0.05,STDEV.S(B5:I5),COUNT(B5:I5))</t>
+  </si>
+  <si>
+    <t>Margin of error for a confidence interval</t>
   </si>
 </sst>
 </file>
@@ -1794,7 +1965,7 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1886,6 +2057,58 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF0432FF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="20"/>
+      <color rgb="FF0432FF"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1920,7 +2143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1938,9 +2161,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1993,6 +2213,44 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2363,13 +2621,13 @@
   <sheetData>
     <row r="1" spans="2:3" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:3" ht="24" x14ac:dyDescent="0.2">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>481</v>
       </c>
-      <c r="C2" s="8"/>
+      <c r="C2" s="25"/>
     </row>
     <row r="3" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="22" t="s">
         <v>482</v>
       </c>
       <c r="C3" s="3"/>
@@ -2387,7 +2645,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="23" t="s">
         <v>494</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -2395,7 +2653,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" ht="25" x14ac:dyDescent="0.2">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>495</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -2403,7 +2661,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>496</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -2411,7 +2669,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>497</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -2419,7 +2677,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>498</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -2427,7 +2685,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="23" t="s">
         <v>499</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -2435,7 +2693,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="23" t="s">
         <v>500</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -2443,7 +2701,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>501</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -2451,7 +2709,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="23" t="s">
         <v>502</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -2459,7 +2717,7 @@
       </c>
     </row>
     <row r="15" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="23" t="s">
         <v>503</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -2467,7 +2725,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" ht="50" x14ac:dyDescent="0.2">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="23" t="s">
         <v>569</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -2510,13 +2768,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -2799,14 +3057,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -2974,7 +3232,7 @@
       <c r="C13" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <f>MOD(B4,5)</f>
         <v>2.2999999999999972</v>
       </c>
@@ -3012,7 +3270,7 @@
       <c r="C15" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <f>SQRT(B5)</f>
         <v>2.8284271247461903</v>
       </c>
@@ -3033,7 +3291,7 @@
       </c>
       <c r="D16" s="3">
         <f ca="1">RANDBETWEEN(1,100)</f>
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>466</v>
@@ -3102,13 +3360,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>525</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="24" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
@@ -3389,13 +3647,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
@@ -3729,13 +3987,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -3754,16 +4012,16 @@
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>55</v>
       </c>
       <c r="E4" s="3"/>
@@ -4087,13 +4345,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -4112,16 +4370,16 @@
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>109</v>
       </c>
       <c r="E4" s="3"/>
@@ -4376,10 +4634,10 @@
       <c r="A20" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>152</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -4432,13 +4690,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -4460,7 +4718,7 @@
       <c r="A4" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <v>45306</v>
       </c>
       <c r="C4" s="3"/>
@@ -4471,7 +4729,7 @@
       <c r="A5" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>45565</v>
       </c>
       <c r="C5" s="3"/>
@@ -4512,7 +4770,7 @@
       <c r="C8" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f ca="1">TODAY()</f>
         <v>46174</v>
       </c>
@@ -4530,9 +4788,9 @@
       <c r="C9" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f ca="1">NOW()</f>
-        <v>46174.763105208331</v>
+        <v>46174.802494560186</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>166</v>
@@ -4548,7 +4806,7 @@
       <c r="C10" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>DATE(2025,12,31)</f>
         <v>46022</v>
       </c>
@@ -4620,7 +4878,7 @@
       <c r="C14" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>EOMONTH(B4,0)</f>
         <v>45322</v>
       </c>
@@ -4638,7 +4896,7 @@
       <c r="C15" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>EDATE(B4,3)</f>
         <v>45397</v>
       </c>
@@ -4674,7 +4932,7 @@
       <c r="C17" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="13">
         <f>YEARFRAC(B4,B5)</f>
         <v>0.70833333333333337</v>
       </c>
@@ -4707,13 +4965,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -4735,7 +4993,7 @@
       <c r="A4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>0.08</v>
       </c>
       <c r="C4" s="3"/>
@@ -4757,7 +5015,7 @@
       <c r="A6" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>100000</v>
       </c>
       <c r="C6" s="3"/>
@@ -4792,10 +5050,10 @@
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>45292</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>-100000</v>
       </c>
       <c r="C10" s="3"/>
@@ -4803,10 +5061,10 @@
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>45474</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="16">
         <v>30000</v>
       </c>
       <c r="C11" s="3"/>
@@ -4814,10 +5072,10 @@
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>45658</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>40000</v>
       </c>
       <c r="C12" s="3"/>
@@ -4825,10 +5083,10 @@
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>45901</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
         <v>50000</v>
       </c>
       <c r="C13" s="3"/>
@@ -4869,7 +5127,7 @@
       <c r="C16" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <f>PV(B4,B5,-25000)</f>
         <v>99817.750926952183</v>
       </c>
@@ -4887,7 +5145,7 @@
       <c r="C17" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <f>FV(B4,B5,0,-B6)</f>
         <v>146932.80768000003</v>
       </c>
@@ -4905,7 +5163,7 @@
       <c r="C18" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <f>PMT(B4,B5,B6)</f>
         <v>-25045.645456683658</v>
       </c>
@@ -4923,7 +5181,7 @@
       <c r="C19" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <f>IPMT(B4,1,B5,B6)</f>
         <v>-8000</v>
       </c>
@@ -4941,7 +5199,7 @@
       <c r="C20" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <f>PPMT(B4,1,B5,B6)</f>
         <v>-17045.645456683658</v>
       </c>
@@ -4959,7 +5217,7 @@
       <c r="C21" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <f>NPV(B4,B11:B13)+B10</f>
         <v>1762.9426408575673</v>
       </c>
@@ -4977,7 +5235,7 @@
       <c r="C22" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="17">
         <f>XNPV(B4,B10:B13,A10:A13)</f>
         <v>9874.4664832622948</v>
       </c>
@@ -4995,7 +5253,7 @@
       <c r="C23" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="18">
         <f>IRR(B10:B13)</f>
         <v>8.8963394693349906E-2</v>
       </c>
@@ -5013,7 +5271,7 @@
       <c r="C24" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="18">
         <f>XIRR(B10:B13,A10:A13)</f>
         <v>0.1740945398807526</v>
       </c>
@@ -5031,7 +5289,7 @@
       <c r="C25" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="18">
         <f>RATE(B5,-25000,B6)</f>
         <v>7.9308261160528359E-2</v>
       </c>
@@ -5059,7 +5317,7 @@
       <c r="A28" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="15">
         <v>50000</v>
       </c>
       <c r="C28" s="3"/>
@@ -5070,7 +5328,7 @@
       <c r="A29" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="15">
         <v>5000</v>
       </c>
       <c r="C29" s="3"/>
@@ -5133,7 +5391,7 @@
       <c r="C34" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="17">
         <f>SLN(B28,B29,B30)</f>
         <v>9000</v>
       </c>
@@ -5151,7 +5409,7 @@
       <c r="C35" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="17">
         <f>DB(B28,B29,B30,B31)</f>
         <v>18450</v>
       </c>
@@ -5169,7 +5427,7 @@
       <c r="C36" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="17">
         <f>DDB(B28,B29,B30,B31)</f>
         <v>20000</v>
       </c>
@@ -5187,7 +5445,7 @@
       <c r="C37" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="17">
         <f>SYD(B28,B29,B30,B31)</f>
         <v>15000</v>
       </c>
@@ -5208,455 +5466,825 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="24" defaultRowHeight="27" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="24" style="1"/>
+    <col min="1" max="1" width="33" style="29" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="15" style="29" customWidth="1"/>
+    <col min="5" max="5" width="50" style="29" customWidth="1"/>
+    <col min="6" max="16384" width="24" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" ht="50" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+    </row>
+    <row r="3" spans="1:9" ht="84" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+    </row>
+    <row r="4" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A4" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="32">
         <v>2.1</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="32">
         <v>-1.4</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="32">
         <v>3.8</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="32">
         <v>0.9</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="32">
         <v>5.2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="32">
         <v>-2.7</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="32">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="32">
         <v>1.6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A5" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="32">
         <v>120</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="32">
         <v>135</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="32">
         <v>150</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="32">
         <v>162</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="32">
         <v>158</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="32">
         <v>175</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="32">
         <v>190</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="32">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A7" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+    </row>
+    <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="28">
         <f>COUNT(B4:I4)</f>
         <v>8</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A9" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="28">
         <f>COUNTA(A4:I4)</f>
         <v>9</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+    </row>
+    <row r="10" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="34" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="35">
         <f>_xlfn.STDEV.S(B4:I4)</f>
         <v>2.7702178872531205</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+    </row>
+    <row r="11" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A11" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="35">
         <f>_xlfn.STDEV.P(B4:I4)</f>
         <v>2.591301555203485</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+    </row>
+    <row r="12" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A12" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="34" t="s">
         <v>269</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="35">
         <f>_xlfn.VAR.S(B4:I4)</f>
         <v>7.6741071428571432</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+    </row>
+    <row r="13" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A13" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="36">
         <f>_xlfn.PERCENTILE.INC(B5:I5,0.9)</f>
         <v>194.5</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+    </row>
+    <row r="14" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A14" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="36">
         <f>_xlfn.QUARTILE.INC(B5:I5,3)</f>
         <v>178.75</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+    </row>
+    <row r="15" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A15" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="28">
         <f>_xlfn.RANK.EQ(F4,B4:I4)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+    </row>
+    <row r="16" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A16" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="36">
         <f>LARGE(B4:I4,2)</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+    </row>
+    <row r="17" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A17" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="36">
         <f>SMALL(B4:I4,2)</f>
         <v>-1.4</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+    </row>
+    <row r="18" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A18" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="D18" s="20" t="str">
+      <c r="D18" s="36" t="str">
         <f>IFERROR(_xlfn.MODE.SNGL(B4:I4),"no repeat")</f>
         <v>no repeat</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+    </row>
+    <row r="19" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A19" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="35">
         <f>CORREL(B4:I4,B5:I5)</f>
         <v>7.7287698452881345E-2</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+    </row>
+    <row r="20" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A20" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="35">
         <f>SLOPE(B5:I5,B4:I4)</f>
         <v>0.77882489819662626</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" ht="50" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+    </row>
+    <row r="21" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A21" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="36">
         <f>_xlfn.FORECAST.LINEAR(3,B5:I5,B4:I4)</f>
         <v>162.85826643397323</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+    </row>
+    <row r="22" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A22" s="28" t="s">
+        <v>570</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="D22" s="35">
+        <f>INDEX(LINEST(B5:I5,B4:I4),1,1)</f>
+        <v>0.77882489819662537</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>573</v>
+      </c>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+    </row>
+    <row r="23" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A23" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>575</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>576</v>
+      </c>
+      <c r="D23" s="35">
+        <f>INDEX(LINEST(B5:I5,B4:I4),1,2)</f>
+        <v>160.52179173938336</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>577</v>
+      </c>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+    </row>
+    <row r="24" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A24" s="28" t="s">
+        <v>578</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="D24" s="37">
+        <f>INDEX(LINEST(B5:I5,B4:I4,TRUE,TRUE),3,1)</f>
+        <v>5.9733883321436152E-3</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+    </row>
+    <row r="25" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A25" s="28" t="s">
+        <v>582</v>
+      </c>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="28" t="s">
+        <v>583</v>
+      </c>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="38" t="s">
+        <v>584</v>
+      </c>
+      <c r="B27" s="39" cm="1">
+        <f t="array" ref="B27:C31">LINEST(B5:I5,B4:I4,TRUE,TRUE)</f>
+        <v>0.77882489819662537</v>
+      </c>
+      <c r="C27" s="39">
+        <v>160.52179173938336</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>585</v>
+      </c>
+      <c r="E27" s="26"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B28" s="39">
+        <v>4.1015955458275846</v>
+      </c>
+      <c r="C28" s="39">
+        <v>12.796550846313563</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>586</v>
+      </c>
+      <c r="E28" s="26"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B29" s="39">
+        <v>5.9733883321436152E-3</v>
+      </c>
+      <c r="C29" s="39">
+        <v>30.061855435423194</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>587</v>
+      </c>
+      <c r="E29" s="26"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B30" s="39">
+        <v>3.6055704718735801E-2</v>
+      </c>
+      <c r="C30" s="39">
+        <v>6</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>588</v>
+      </c>
+      <c r="E30" s="26"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B31" s="39">
+        <v>32.584086678301901</v>
+      </c>
+      <c r="C31" s="39">
+        <v>5422.2909133216981</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>589</v>
+      </c>
+      <c r="E31" s="26"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+    </row>
+    <row r="36" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A36" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A37" s="28" t="s">
+        <v>591</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>593</v>
+      </c>
+      <c r="D37" s="37">
+        <f>_xlfn.NORM.DIST(160,AVERAGE(B5:I5),_xlfn.STDEV.S(B5:I5),TRUE)</f>
+        <v>0.47322425858499539</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+    </row>
+    <row r="38" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A38" s="28" t="s">
+        <v>595</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>596</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>597</v>
+      </c>
+      <c r="D38" s="35">
+        <f>_xlfn.NORM.INV(0.9,AVERAGE(B5:I5),_xlfn.STDEV.S(B5:I5))</f>
+        <v>197.64998555024238</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>598</v>
+      </c>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+    </row>
+    <row r="39" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A39" s="28" t="s">
+        <v>599</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>600</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>601</v>
+      </c>
+      <c r="D39" s="37">
+        <f>_xlfn.NORM.S.DIST(1.5,TRUE)</f>
+        <v>0.93319279873114191</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+    </row>
+    <row r="40" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A40" s="28" t="s">
+        <v>603</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="D40" s="37">
+        <f>_xlfn.NORM.S.INV(0.975)</f>
+        <v>1.9599639845400536</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+    </row>
+    <row r="41" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A41" s="28" t="s">
+        <v>607</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>608</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>609</v>
+      </c>
+      <c r="D41" s="37">
+        <f>STANDARDIZE(160,AVERAGE(B5:I5),_xlfn.STDEV.S(B5:I5))</f>
+        <v>-6.7167299956599036E-2</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>610</v>
+      </c>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+    </row>
+    <row r="42" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A42" s="28" t="s">
+        <v>611</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>612</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>613</v>
+      </c>
+      <c r="D42" s="37">
+        <f>_xlfn.BINOM.DIST(3,10,0.5,FALSE)</f>
+        <v>0.11718750000000003</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>614</v>
+      </c>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+    </row>
+    <row r="43" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A43" s="28" t="s">
+        <v>615</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>617</v>
+      </c>
+      <c r="D43" s="37">
+        <f>_xlfn.POISSON.DIST(4,3,FALSE)</f>
+        <v>0.16803135574154085</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+    </row>
+    <row r="44" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A44" s="28" t="s">
+        <v>619</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>620</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>621</v>
+      </c>
+      <c r="D44" s="37">
+        <f>_xlfn.EXPON.DIST(2,0.5,TRUE)</f>
+        <v>0.63212055882855767</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>622</v>
+      </c>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+    </row>
+    <row r="45" spans="1:9" ht="56" x14ac:dyDescent="0.35">
+      <c r="A45" s="28" t="s">
+        <v>623</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>624</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>625</v>
+      </c>
+      <c r="D45" s="35">
+        <f>_xlfn.CONFIDENCE.NORM(0.05,_xlfn.STDEV.S(B5:I5),COUNT(B5:I5))</f>
+        <v>19.344008709109509</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A34:E34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5679,13 +6307,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
@@ -5990,7 +6618,7 @@
       <c r="C22" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13">
         <f>VALUE(B6)</f>
         <v>1250.75</v>
       </c>
@@ -6024,23 +6652,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="300" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>365</v>
       </c>
       <c r="B2" s="3"/>
@@ -6070,10 +6698,10 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>366</v>
       </c>
       <c r="C4" s="3"/>
@@ -6588,7 +7216,7 @@
       <c r="E32" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="19">
         <f>_xlfn.LET(_xlpm.t,SUM(B5:B10),_xlpm.t/COUNT(B5:B10))</f>
         <v>1191.6666666666667</v>
       </c>
